--- a/output/pdf_financials_xlsx/RPP.xlsx
+++ b/output/pdf_financials_xlsx/RPP.xlsx
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.122444</v>
+        <v>-0.122444</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.006132</v>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.122444</v>
+        <v>-0.122444</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>0.005273</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.122444</v>
+        <v>-0.122444</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0.005273</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.122444</v>
+        <v>-0.122444</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>0.006132</v>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.122444</v>
+        <v>-0.122444</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0.006132</v>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>14.00848010437052</v>
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.122444</v>
+        <v>-0.122444</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>0.005273</v>
@@ -71526,10 +71526,10 @@
         </is>
       </c>
       <c r="E596" s="5" t="n">
-        <v>0.122444</v>
+        <v>-0.122444</v>
       </c>
       <c r="F596" s="5" t="n">
-        <v>3.6999e-05</v>
+        <v>-3.6999e-05</v>
       </c>
       <c r="G596" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RPP.xlsx
+++ b/output/pdf_financials_xlsx/RPP.xlsx
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>4.385e-06</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000543</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.001416</v>
@@ -1165,31 +1165,31 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.008855999999999999</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.035826</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001974</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.002556</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.016707</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.061353</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000262</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.00254</v>
       </c>
       <c r="S12" s="1" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.122444</v>
+        <v>-0.122448385</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.006132</v>
+        <v>0.005589</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.057106</v>
@@ -2254,31 +2254,31 @@
         <v>-0.483024</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.803624</v>
+        <v>0.794768</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.967958</v>
+        <v>1.932132</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.342139</v>
+        <v>1.340165</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.019489</v>
+        <v>-1.022045</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.171456</v>
+        <v>-2.188163</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.475878</v>
+        <v>-0.537231</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.031249</v>
+        <v>-0.031511</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.472974</v>
+        <v>0.472722</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.539029</v>
+        <v>0.536489</v>
       </c>
       <c r="S27" s="1" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.122444</v>
+        <v>-0.122448385</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.006132</v>
+        <v>0.005589</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.055403</v>
@@ -2380,31 +2380,31 @@
         <v>-0.483024</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.803624</v>
+        <v>0.794768</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.967958</v>
+        <v>1.932132</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.342139</v>
+        <v>1.340165</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.019489</v>
+        <v>-1.022045</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.171456</v>
+        <v>-2.188163</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.475878</v>
+        <v>-0.537231</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.027879</v>
+        <v>-0.028141</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.47567</v>
+        <v>0.475418</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.5456029999999999</v>
+        <v>0.543063</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>100</v>
+        <v>91.14481409001957</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-295.9561965811966</v>
@@ -2680,36 +2680,34 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.034513</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.192287</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.192287</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.093254</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.07519099999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.256611</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>30.969408</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>31.33734</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>30.020798</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>24.782924</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0</v>
@@ -2724,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.015745</v>
       </c>
     </row>
     <row r="35">
@@ -2814,36 +2812,34 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.034513</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.192287</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.192287</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.093254</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.07519099999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.256611</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>30.969408</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>31.33734</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>30.020798</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>24.782924</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0</v>
@@ -2858,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.015745</v>
       </c>
     </row>
     <row r="37">
@@ -3611,22 +3607,22 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.201285</v>
+        <v>0.008998000000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.201285</v>
+        <v>0.008998000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.10151</v>
+        <v>0.008255999999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.084604</v>
+        <v>0.009412999999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.265194</v>
+        <v>0.008583</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.032572</v>
+        <v>0</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -3637,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>24.763598</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>23.57074</v>
@@ -3652,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>3.23522</v>
+        <v>3.219475</v>
       </c>
     </row>
     <row r="49">
@@ -9938,7 +9934,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -18152,7 +18148,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -19184,7 +19180,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -22230,7 +22226,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -24672,7 +24668,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -51606,7 +51602,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -57540,7 +57536,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -59206,7 +59202,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -60772,7 +60768,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -71310,7 +71306,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E594" s="5" t="n">

--- a/output/pdf_financials_xlsx/RPP.xlsx
+++ b/output/pdf_financials_xlsx/RPP.xlsx
@@ -1459,7 +1459,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.000859</v>
+        <v>0.000859</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0.057106</v>
@@ -1489,7 +1489,7 @@
         <v>0.351999</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.530775</v>
+        <v>-0.530775</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0.136073</v>
@@ -3075,22 +3075,22 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.026237</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.018223</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.001057</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.004089</v>
       </c>
       <c r="L40" s="1" t="inlineStr">
         <is>
@@ -3140,22 +3140,22 @@
         <v>0.058979</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.116727</v>
+        <v>0.142964</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.078988</v>
+        <v>0.09721100000000001</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.06454799999999999</v>
+        <v>0.084548</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.116158</v>
+        <v>0.136158</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.014756</v>
+        <v>0.015813</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.154527</v>
+        <v>0.158616</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>0.11088</v>
@@ -3607,19 +3607,19 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.008998000000000001</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.008998000000000001</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.008255999999999999</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.009412999999999999</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.008583</v>
+        <v>0.007526</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -4929,51 +4929,49 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.236069</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.352147</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.053321</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.06758</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0501</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.044049</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.048171</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.048</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.05497</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.0864</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.05535</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.04012</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.040586</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.04012</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.040118</v>
       </c>
     </row>
     <row r="68">
@@ -29198,7 +29196,11 @@
           <t>Deferred income tax expense (Note 10)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -32114,7 +32116,11 @@
           <t>Deferred income tax expense (Note 11)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -33352,7 +33358,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -35512,7 +35522,11 @@
           <t>Deferred income tax expense (recovery) (Note 13)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -36568,7 +36582,11 @@
           <t>Deferred income tax expense (recovery) (Note 11)</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -37728,7 +37746,11 @@
           <t>Deferred income tax expense (Note 11)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -39304,7 +39326,11 @@
           <t>Deferred income tax expense (Note 10)</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -40992,7 +41018,11 @@
           <t>Deferred income tax expense (Note 10)</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -42768,7 +42798,11 @@
           <t>Deferred income tax expense (Note 13)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -44034,7 +44068,11 @@
           <t>Deferred income tax expense (Note 15)</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -46340,7 +46378,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -49402,7 +49444,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -57958,7 +58004,11 @@
           <t>Deferred income tax recovery (expense) (Note 11)</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -70556,7 +70606,11 @@
           <t>Income taxes recovery (expense)</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
           <t>-</t>
